--- a/research/traditional_assets/database/data/qatar/qatar_brokerage_investment_banking.xlsx
+++ b/research/traditional_assets/database/data/qatar/qatar_brokerage_investment_banking.xlsx
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.07869999999999999</v>
+        <v>0.02699999999999999</v>
       </c>
       <c r="E2">
-        <v>0.312</v>
+        <v>0.292</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,28 +606,28 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>5.77</v>
+        <v>2.609</v>
       </c>
       <c r="L2">
-        <v>0.2649219467401285</v>
+        <v>0.1396680942184154</v>
       </c>
       <c r="M2">
         <v>0.778</v>
       </c>
       <c r="N2">
-        <v>0.004933417882054534</v>
+        <v>0.006294498381877023</v>
       </c>
       <c r="O2">
-        <v>0.1348353552859619</v>
+        <v>0.298198543503258</v>
       </c>
       <c r="P2">
         <v>0.778</v>
       </c>
       <c r="Q2">
-        <v>0.004933417882054534</v>
+        <v>0.006294498381877023</v>
       </c>
       <c r="R2">
-        <v>0.1348353552859619</v>
+        <v>0.298198543503258</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,55 +636,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>39.3</v>
+        <v>36.8</v>
       </c>
       <c r="V2">
-        <v>0.2492073557387444</v>
+        <v>0.2977346278317152</v>
       </c>
       <c r="W2">
-        <v>0.05687559371327982</v>
+        <v>0.03498158243701193</v>
       </c>
       <c r="X2">
-        <v>0.03710491670068062</v>
+        <v>0.07193786468067334</v>
       </c>
       <c r="Y2">
-        <v>0.0197706770125992</v>
+        <v>-0.03695628224366141</v>
       </c>
       <c r="Z2">
-        <v>0.3990472700622939</v>
+        <v>0.2693194925028835</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.03665348572165476</v>
+        <v>0.07083979478091278</v>
       </c>
       <c r="AC2">
-        <v>-0.03665348572165476</v>
+        <v>-0.07083979478091278</v>
       </c>
       <c r="AD2">
-        <v>7.36</v>
+        <v>6.38</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>7.36</v>
+        <v>6.38</v>
       </c>
       <c r="AG2">
-        <v>-31.94</v>
+        <v>-30.42</v>
       </c>
       <c r="AH2">
-        <v>0.04458984611656368</v>
+        <v>0.04908447453454378</v>
       </c>
       <c r="AI2">
-        <v>0.06792174234034699</v>
+        <v>0.05832876211373195</v>
       </c>
       <c r="AJ2">
-        <v>-0.2539758269720102</v>
+        <v>-0.3264649066323245</v>
       </c>
       <c r="AK2">
-        <v>-0.4624963799594555</v>
+        <v>-0.4191237255442271</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0882</v>
+        <v>-0.11</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -725,10 +725,10 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>4.22</v>
+        <v>-0.451</v>
       </c>
       <c r="L3">
-        <v>0.2588957055214723</v>
+        <v>-0.04587995930824008</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -737,7 +737,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -746,37 +746,37 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>24</v>
+        <v>20.2</v>
       </c>
       <c r="V3">
-        <v>0.2492211838006231</v>
+        <v>0.338358458961474</v>
       </c>
       <c r="W3">
-        <v>0.07390542907180385</v>
+        <v>-0.007309562398703403</v>
       </c>
       <c r="X3">
-        <v>0.03597869151659337</v>
+        <v>0.07051301243196936</v>
       </c>
       <c r="Y3">
-        <v>0.03792673755521048</v>
+        <v>-0.07782257483067277</v>
       </c>
       <c r="Z3">
-        <v>0.552542372881356</v>
+        <v>0.2607427055702918</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.03597869151659337</v>
+        <v>0.07051301243196936</v>
       </c>
       <c r="AC3">
-        <v>-0.03597869151659337</v>
+        <v>-0.07051301243196936</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -788,7 +788,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-24</v>
+        <v>-20.2</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -797,10 +797,10 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.3319502074688797</v>
+        <v>-0.5113924050632911</v>
       </c>
       <c r="AK3">
-        <v>-0.6417112299465241</v>
+        <v>-0.4926829268292683</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0692</v>
+        <v>0.164</v>
       </c>
       <c r="E4">
-        <v>0.312</v>
+        <v>0.292</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -844,28 +844,28 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>1.55</v>
+        <v>3.06</v>
       </c>
       <c r="L4">
-        <v>0.2828467153284671</v>
+        <v>0.3457627118644068</v>
       </c>
       <c r="M4">
         <v>0.778</v>
       </c>
       <c r="N4">
-        <v>0.01267100977198697</v>
+        <v>0.01217527386541471</v>
       </c>
       <c r="O4">
-        <v>0.5019354838709678</v>
+        <v>0.2542483660130719</v>
       </c>
       <c r="P4">
         <v>0.778</v>
       </c>
       <c r="Q4">
-        <v>0.01267100977198697</v>
+        <v>0.01217527386541471</v>
       </c>
       <c r="R4">
-        <v>0.5019354838709678</v>
+        <v>0.2542483660130719</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -874,55 +874,55 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>15.3</v>
+        <v>16.6</v>
       </c>
       <c r="V4">
-        <v>0.249185667752443</v>
+        <v>0.2597809076682316</v>
       </c>
       <c r="W4">
-        <v>0.03984575835475579</v>
+        <v>0.07727272727272727</v>
       </c>
       <c r="X4">
-        <v>0.03823114188476787</v>
+        <v>0.07336271692937732</v>
       </c>
       <c r="Y4">
-        <v>0.001614616469987916</v>
+        <v>0.003910010343349951</v>
       </c>
       <c r="Z4">
-        <v>0.2185007974481659</v>
+        <v>0.2795325331648768</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.03732827992671615</v>
+        <v>0.07116657712985619</v>
       </c>
       <c r="AC4">
-        <v>-0.03732827992671615</v>
+        <v>-0.07116657712985619</v>
       </c>
       <c r="AD4">
-        <v>7.36</v>
+        <v>6.38</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>7.36</v>
+        <v>6.38</v>
       </c>
       <c r="AG4">
-        <v>-7.94</v>
+        <v>-10.22</v>
       </c>
       <c r="AH4">
-        <v>0.1070389761489238</v>
+        <v>0.09077973819009676</v>
       </c>
       <c r="AI4">
-        <v>0.1567291311754685</v>
+        <v>0.1324200913242009</v>
       </c>
       <c r="AJ4">
-        <v>-0.1485222596333708</v>
+        <v>-0.190387481371088</v>
       </c>
       <c r="AK4">
-        <v>-0.2507896399241946</v>
+        <v>-0.3236225459151363</v>
       </c>
       <c r="AL4">
         <v>0</v>

--- a/research/traditional_assets/database/data/qatar/qatar_brokerage_investment_banking.xlsx
+++ b/research/traditional_assets/database/data/qatar/qatar_brokerage_investment_banking.xlsx
@@ -588,10 +588,7 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.02699999999999999</v>
-      </c>
-      <c r="E2">
-        <v>0.292</v>
+        <v>0.04049999999999999</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,28 +603,28 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>2.609</v>
+        <v>-10.03</v>
       </c>
       <c r="L2">
-        <v>0.1396680942184154</v>
+        <v>-0.8767482517482518</v>
       </c>
       <c r="M2">
         <v>0.778</v>
       </c>
       <c r="N2">
-        <v>0.006294498381877023</v>
+        <v>0.005827715355805244</v>
       </c>
       <c r="O2">
-        <v>0.298198543503258</v>
+        <v>-0.07756729810568294</v>
       </c>
       <c r="P2">
         <v>0.778</v>
       </c>
       <c r="Q2">
-        <v>0.006294498381877023</v>
+        <v>0.005827715355805244</v>
       </c>
       <c r="R2">
-        <v>0.298198543503258</v>
+        <v>-0.07756729810568294</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,55 +633,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>36.8</v>
+        <v>31.6</v>
       </c>
       <c r="V2">
-        <v>0.2977346278317152</v>
+        <v>0.2367041198501872</v>
       </c>
       <c r="W2">
-        <v>0.03498158243701193</v>
+        <v>-0.07476271054576575</v>
       </c>
       <c r="X2">
-        <v>0.07193786468067334</v>
+        <v>0.06134973861270076</v>
       </c>
       <c r="Y2">
-        <v>-0.03695628224366141</v>
+        <v>-0.1361124491584665</v>
       </c>
       <c r="Z2">
-        <v>0.2693194925028835</v>
+        <v>0.1569703622392975</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.07083979478091278</v>
+        <v>0.06066592807205264</v>
       </c>
       <c r="AC2">
-        <v>-0.07083979478091278</v>
+        <v>-0.06066592807205264</v>
       </c>
       <c r="AD2">
-        <v>6.38</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>6.38</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="AG2">
-        <v>-30.42</v>
+        <v>-22.49</v>
       </c>
       <c r="AH2">
-        <v>0.04908447453454378</v>
+        <v>0.0638805132879882</v>
       </c>
       <c r="AI2">
-        <v>0.05832876211373195</v>
+        <v>0.09009989120759568</v>
       </c>
       <c r="AJ2">
-        <v>-0.3264649066323245</v>
+        <v>-0.2025943608683902</v>
       </c>
       <c r="AK2">
-        <v>-0.4191237255442271</v>
+        <v>-0.3235505682635592</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -710,7 +707,7 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.11</v>
+        <v>-0.186</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -725,10 +722,10 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>-0.451</v>
+        <v>-11.8</v>
       </c>
       <c r="L3">
-        <v>-0.04587995930824008</v>
+        <v>-2.789598108747045</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -752,31 +749,31 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>20.2</v>
+        <v>18.9</v>
       </c>
       <c r="V3">
-        <v>0.338358458961474</v>
+        <v>0.2739130434782608</v>
       </c>
       <c r="W3">
-        <v>-0.007309562398703403</v>
+        <v>-0.191869918699187</v>
       </c>
       <c r="X3">
-        <v>0.07051301243196936</v>
+        <v>0.06000216824494638</v>
       </c>
       <c r="Y3">
-        <v>-0.07782257483067277</v>
+        <v>-0.2518720869441334</v>
       </c>
       <c r="Z3">
-        <v>0.2607427055702918</v>
+        <v>0.1024213075060533</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.07051301243196936</v>
+        <v>0.06000216824494638</v>
       </c>
       <c r="AC3">
-        <v>-0.07051301243196936</v>
+        <v>-0.06000216824494638</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -788,7 +785,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-20.2</v>
+        <v>-18.9</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -797,10 +794,10 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.5113924050632911</v>
+        <v>-0.3772455089820359</v>
       </c>
       <c r="AK3">
-        <v>-0.4926829268292683</v>
+        <v>-0.6057692307692306</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -817,7 +814,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Islamic Holding Group (Q.P.S.C) (DSM:IHGS)</t>
+          <t>INMA Holding Company Q.P.S.C. (DSM:IHGS)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -826,10 +823,7 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.164</v>
-      </c>
-      <c r="E4">
-        <v>0.292</v>
+        <v>0.267</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -844,28 +838,28 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>3.06</v>
+        <v>1.77</v>
       </c>
       <c r="L4">
-        <v>0.3457627118644068</v>
+        <v>0.2454923717059639</v>
       </c>
       <c r="M4">
         <v>0.778</v>
       </c>
       <c r="N4">
-        <v>0.01217527386541471</v>
+        <v>0.01206201550387597</v>
       </c>
       <c r="O4">
-        <v>0.2542483660130719</v>
+        <v>0.43954802259887</v>
       </c>
       <c r="P4">
         <v>0.778</v>
       </c>
       <c r="Q4">
-        <v>0.01217527386541471</v>
+        <v>0.01206201550387597</v>
       </c>
       <c r="R4">
-        <v>0.2542483660130719</v>
+        <v>0.43954802259887</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -874,55 +868,55 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>16.6</v>
+        <v>12.7</v>
       </c>
       <c r="V4">
-        <v>0.2597809076682316</v>
+        <v>0.1968992248062015</v>
       </c>
       <c r="W4">
-        <v>0.07727272727272727</v>
+        <v>0.0423444976076555</v>
       </c>
       <c r="X4">
-        <v>0.07336271692937732</v>
+        <v>0.06269730898045514</v>
       </c>
       <c r="Y4">
-        <v>0.003910010343349951</v>
+        <v>-0.02035281137279964</v>
       </c>
       <c r="Z4">
-        <v>0.2795325331648768</v>
+        <v>0.2283090563647878</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.07116657712985619</v>
+        <v>0.06132968789915889</v>
       </c>
       <c r="AC4">
-        <v>-0.07116657712985619</v>
+        <v>-0.06132968789915889</v>
       </c>
       <c r="AD4">
-        <v>6.38</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>6.38</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="AG4">
-        <v>-10.22</v>
+        <v>-3.59</v>
       </c>
       <c r="AH4">
-        <v>0.09077973819009676</v>
+        <v>0.123760358646923</v>
       </c>
       <c r="AI4">
-        <v>0.1324200913242009</v>
+        <v>0.1785924328563027</v>
       </c>
       <c r="AJ4">
-        <v>-0.190387481371088</v>
+        <v>-0.05893941881464456</v>
       </c>
       <c r="AK4">
-        <v>-0.3236225459151363</v>
+        <v>-0.09370921430435916</v>
       </c>
       <c r="AL4">
         <v>0</v>
